--- a/database/event/2407/event_2407_evp_summary.xlsx
+++ b/database/event/2407/event_2407_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.2194</v>
+        <v>9.1752</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7526</v>
+        <v>5.725</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3031</v>
+        <v>3.2115</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2194</v>
+        <v>9.1752</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9794</v>
+        <v>2.9352</v>
       </c>
       <c r="G2" t="n">
         <v>6.24</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9794</v>
+        <v>2.9352</v>
       </c>
       <c r="I2" t="n">
         <v>3.0353</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.489800000000001</v>
+        <v>8.4367</v>
       </c>
       <c r="C3" t="n">
-        <v>5.2973</v>
+        <v>5.2642</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0083</v>
+        <v>2.9173</v>
       </c>
       <c r="E3" t="n">
-        <v>8.489800000000001</v>
+        <v>8.4367</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5767</v>
+        <v>3.5236</v>
       </c>
       <c r="G3" t="n">
         <v>4.9131</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5767</v>
+        <v>3.5236</v>
       </c>
       <c r="I3" t="n">
         <v>3.6437</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.118399999999999</v>
+        <v>8.0862</v>
       </c>
       <c r="C4" t="n">
-        <v>5.0656</v>
+        <v>5.0455</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8583</v>
+        <v>2.7776</v>
       </c>
       <c r="E4" t="n">
-        <v>8.118399999999999</v>
+        <v>8.0862</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1724</v>
+        <v>2.1402</v>
       </c>
       <c r="G4" t="n">
         <v>5.946</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1724</v>
+        <v>2.1402</v>
       </c>
       <c r="I4" t="n">
         <v>2.2131</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1018</v>
+        <v>6.0557</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8073</v>
+        <v>3.7785</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0436</v>
+        <v>1.9687</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1018</v>
+        <v>6.0557</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1062</v>
+        <v>3.0601</v>
       </c>
       <c r="G5" t="n">
         <v>2.9956</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1062</v>
+        <v>3.0601</v>
       </c>
       <c r="I5" t="n">
         <v>3.1644</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8466</v>
+        <v>5.7939</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6481</v>
+        <v>3.6152</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9405</v>
+        <v>1.8644</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8466</v>
+        <v>5.7939</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5534</v>
+        <v>3.5007</v>
       </c>
       <c r="G6" t="n">
         <v>2.2932</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5534</v>
+        <v>3.5007</v>
       </c>
       <c r="I6" t="n">
         <v>3.62</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5892</v>
+        <v>4.8736</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8635</v>
+        <v>3.0409</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4326</v>
+        <v>1.4977</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5892</v>
+        <v>4.8736</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7602</v>
+        <v>0.7776</v>
       </c>
       <c r="G7" t="n">
-        <v>3.829</v>
+        <v>4.096</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7602</v>
+        <v>0.7776</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7673</v>
+        <v>0.7907</v>
       </c>
       <c r="J7" t="n">
-        <v>3.829</v>
+        <v>4.096</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>202</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5963</v>
+        <v>4.8867</v>
       </c>
       <c r="N7" t="n">
         <v>253</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5664</v>
+        <v>4.6842</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8493</v>
+        <v>2.9228</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4234</v>
+        <v>1.4223</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5664</v>
+        <v>4.6842</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4704</v>
+        <v>0.8551</v>
       </c>
       <c r="G8" t="n">
-        <v>4.096</v>
+        <v>3.829</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4704</v>
+        <v>0.8551</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4748</v>
+        <v>0.8696</v>
       </c>
       <c r="J8" t="n">
-        <v>4.096</v>
+        <v>3.829</v>
       </c>
       <c r="K8" t="n">
         <v>51</v>
@@ -805,7 +805,7 @@
         <v>202</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5708</v>
+        <v>4.6986</v>
       </c>
       <c r="N8" t="n">
         <v>253</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3644</v>
+        <v>4.3586</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7232</v>
+        <v>2.7196</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3418</v>
+        <v>1.2926</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3644</v>
+        <v>4.3586</v>
       </c>
       <c r="F9" t="n">
-        <v>0.774</v>
+        <v>0.7682</v>
       </c>
       <c r="G9" t="n">
         <v>3.5904</v>
       </c>
       <c r="H9" t="n">
-        <v>0.774</v>
+        <v>0.7682</v>
       </c>
       <c r="I9" t="n">
         <v>0.7812</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1844</v>
+        <v>4.1497</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6109</v>
+        <v>2.5893</v>
       </c>
       <c r="D10" t="n">
-        <v>1.269</v>
+        <v>1.2093</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1844</v>
+        <v>4.1497</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3383</v>
+        <v>2.3036</v>
       </c>
       <c r="G10" t="n">
         <v>1.8461</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3383</v>
+        <v>2.3036</v>
       </c>
       <c r="I10" t="n">
         <v>2.3821</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5313</v>
+        <v>3.569</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2034</v>
+        <v>2.2269</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0052</v>
+        <v>0.978</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5313</v>
+        <v>3.569</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6351</v>
+        <v>1.93</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8962</v>
+        <v>1.639</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6351</v>
+        <v>1.93</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6581</v>
+        <v>1.9626</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8962</v>
+        <v>1.639</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5543</v>
+        <v>3.6016</v>
       </c>
       <c r="N11" t="n">
-        <v>230</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.054</v>
+        <v>3.5131</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9056</v>
+        <v>2.192</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8124</v>
+        <v>0.9557</v>
       </c>
       <c r="E12" t="n">
-        <v>3.054</v>
+        <v>3.5131</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7279</v>
+        <v>1.6169</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3261</v>
+        <v>1.8962</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7279</v>
+        <v>1.6169</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7522</v>
+        <v>1.6581</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3261</v>
+        <v>1.8962</v>
       </c>
       <c r="K12" t="n">
         <v>103</v>
@@ -989,7 +989,7 @@
         <v>127</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0783</v>
+        <v>3.5543</v>
       </c>
       <c r="N12" t="n">
         <v>230</v>
@@ -998,219 +998,219 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7024</v>
+        <v>3.2397</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6862</v>
+        <v>2.0214</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6703</v>
+        <v>0.8468</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7024</v>
+        <v>3.2397</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3324</v>
+        <v>3.3108</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>-0.0711</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3324</v>
+        <v>3.3108</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3511</v>
+        <v>3.3668</v>
       </c>
       <c r="J13" t="n">
-        <v>1.37</v>
+        <v>-0.0711</v>
       </c>
       <c r="K13" t="n">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="L13" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7211</v>
+        <v>3.2957</v>
       </c>
       <c r="N13" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6613</v>
+        <v>3.0348</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6605</v>
+        <v>1.8936</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.7652</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6613</v>
+        <v>3.0348</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0223</v>
+        <v>1.7087</v>
       </c>
       <c r="G14" t="n">
-        <v>1.639</v>
+        <v>1.3261</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0223</v>
+        <v>1.7087</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0319</v>
+        <v>1.7522</v>
       </c>
       <c r="J14" t="n">
-        <v>1.639</v>
+        <v>1.3261</v>
       </c>
       <c r="K14" t="n">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6709</v>
+        <v>3.0783</v>
       </c>
       <c r="N14" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1409</v>
+        <v>2.8035</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3358</v>
+        <v>1.7493</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4435</v>
+        <v>0.673</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1409</v>
+        <v>2.8035</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1409</v>
+        <v>1.4335</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1409</v>
+        <v>1.4335</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1609</v>
+        <v>1.47</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="K15" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1609</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>108</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8922</v>
+        <v>2.6766</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1807</v>
+        <v>1.6701</v>
       </c>
       <c r="D16" t="n">
-        <v>0.343</v>
+        <v>0.6224</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8922</v>
+        <v>2.6766</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2557</v>
+        <v>2.3989</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3635</v>
+        <v>0.2777</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2557</v>
+        <v>2.3989</v>
       </c>
       <c r="I16" t="n">
-        <v>2.298</v>
+        <v>2.4394</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3635</v>
+        <v>0.2777</v>
       </c>
       <c r="K16" t="n">
-        <v>209</v>
+        <v>40</v>
       </c>
       <c r="L16" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9345</v>
+        <v>2.7171</v>
       </c>
       <c r="N16" t="n">
-        <v>332</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.866</v>
+        <v>2.2956</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1643</v>
+        <v>1.4324</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3325</v>
+        <v>0.4707</v>
       </c>
       <c r="E17" t="n">
-        <v>1.866</v>
+        <v>2.2956</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3134</v>
+        <v>2.1336</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5526</v>
+        <v>0.162</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3134</v>
+        <v>2.1336</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3257</v>
+        <v>2.1697</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5526</v>
+        <v>0.162</v>
       </c>
       <c r="K17" t="n">
         <v>47</v>
@@ -1219,7 +1219,7 @@
         <v>72</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8783</v>
+        <v>2.3317</v>
       </c>
       <c r="N17" t="n">
         <v>119</v>
@@ -1228,173 +1228,173 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8283</v>
+        <v>2.1395</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1408</v>
+        <v>1.335</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3172</v>
+        <v>0.4085</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8283</v>
+        <v>2.1395</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5506</v>
+        <v>2.1395</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2777</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5506</v>
+        <v>2.1395</v>
       </c>
       <c r="I18" t="n">
-        <v>1.565</v>
+        <v>2.1757</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2777</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="L18" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8427</v>
+        <v>2.1757</v>
       </c>
       <c r="N18" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7534</v>
+        <v>2.1249</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0941</v>
+        <v>1.3259</v>
       </c>
       <c r="D19" t="n">
-        <v>0.287</v>
+        <v>0.4027</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7534</v>
+        <v>2.1249</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7534</v>
+        <v>2.1249</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7534</v>
+        <v>2.1249</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7697</v>
+        <v>2.1609</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7697</v>
+        <v>2.1609</v>
       </c>
       <c r="N19" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7149</v>
+        <v>2.0128</v>
       </c>
       <c r="C20" t="n">
-        <v>1.07</v>
+        <v>1.2559</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2714</v>
+        <v>0.358</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7149</v>
+        <v>2.0128</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0797</v>
+        <v>1.4602</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6352</v>
+        <v>0.5526</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0797</v>
+        <v>1.4602</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0898</v>
+        <v>1.4849</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6352</v>
+        <v>0.5526</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L20" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.725</v>
+        <v>2.0375</v>
       </c>
       <c r="N20" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6435</v>
+        <v>1.8587</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0255</v>
+        <v>1.1598</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2426</v>
+        <v>0.2966</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6435</v>
+        <v>1.8587</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0277</v>
+        <v>2.2222</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3842</v>
+        <v>-0.3635</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0277</v>
+        <v>2.2222</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0845</v>
+        <v>2.298</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3842</v>
+        <v>-0.3635</v>
       </c>
       <c r="K21" t="n">
         <v>209</v>
@@ -1403,7 +1403,7 @@
         <v>123</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7003</v>
+        <v>1.9345</v>
       </c>
       <c r="N21" t="n">
         <v>332</v>
@@ -1412,446 +1412,446 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6246</v>
+        <v>1.7243</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0137</v>
+        <v>1.0759</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2349</v>
+        <v>0.2431</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6246</v>
+        <v>1.7243</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6957</v>
+        <v>1.0891</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0711</v>
+        <v>0.6352</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6957</v>
+        <v>1.0891</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7115</v>
+        <v>1.1075</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0711</v>
+        <v>0.6352</v>
       </c>
       <c r="K22" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6404</v>
+        <v>1.7427</v>
       </c>
       <c r="N22" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5808</v>
+        <v>1.7065</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9864000000000001</v>
+        <v>1.0648</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2172</v>
+        <v>0.236</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5808</v>
+        <v>1.7065</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5808</v>
+        <v>1.3873</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.3192</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5808</v>
+        <v>1.3873</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5955</v>
+        <v>1.4226</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.3192</v>
       </c>
       <c r="K23" t="n">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5955</v>
+        <v>1.7418</v>
       </c>
       <c r="N23" t="n">
-        <v>117</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4892</v>
+        <v>1.6417</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9292</v>
+        <v>1.0244</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1802</v>
+        <v>0.2101</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4892</v>
+        <v>1.6417</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4892</v>
+        <v>1.8082</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.1665</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4892</v>
+        <v>1.8082</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5031</v>
+        <v>1.8388</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.1665</v>
       </c>
       <c r="K24" t="n">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5031</v>
+        <v>1.6723</v>
       </c>
       <c r="N24" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4558</v>
+        <v>1.5986</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9084</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1667</v>
+        <v>0.193</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4558</v>
+        <v>1.5986</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4558</v>
+        <v>2.9828</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1.3842</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4558</v>
+        <v>2.9828</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4693</v>
+        <v>3.0845</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1.3842</v>
       </c>
       <c r="K25" t="n">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4693</v>
+        <v>1.7003</v>
       </c>
       <c r="N25" t="n">
-        <v>117</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3963</v>
+        <v>1.569</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8712</v>
+        <v>0.979</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1427</v>
+        <v>0.1812</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3963</v>
+        <v>1.569</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2343</v>
+        <v>1.569</v>
       </c>
       <c r="G26" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2343</v>
+        <v>1.569</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2458</v>
+        <v>1.5955</v>
       </c>
       <c r="J26" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="L26" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4078</v>
+        <v>1.5955</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3841</v>
+        <v>1.4901</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8636</v>
+        <v>0.9298</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1378</v>
+        <v>0.1497</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3841</v>
+        <v>1.4901</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3841</v>
+        <v>2.2222</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.7321</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3841</v>
+        <v>2.2222</v>
       </c>
       <c r="I27" t="n">
-        <v>1.397</v>
+        <v>2.2598</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.7321</v>
       </c>
       <c r="K27" t="n">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M27" t="n">
-        <v>1.397</v>
+        <v>1.5277</v>
       </c>
       <c r="N27" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3618</v>
+        <v>1.4781</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8497</v>
+        <v>0.9223</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1288</v>
+        <v>0.145</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3618</v>
+        <v>1.4781</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0426</v>
+        <v>1.4781</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3192</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0426</v>
+        <v>1.4781</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0572</v>
+        <v>1.5031</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3192</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="L28" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3764</v>
+        <v>1.5031</v>
       </c>
       <c r="N28" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3264</v>
+        <v>1.4514</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8276</v>
+        <v>0.9056</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1145</v>
+        <v>0.1343</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3264</v>
+        <v>1.4514</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3264</v>
+        <v>2.3666</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.9152</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3264</v>
+        <v>2.3666</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3326</v>
+        <v>2.4269</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.9152</v>
       </c>
       <c r="K29" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3326</v>
+        <v>1.5117</v>
       </c>
       <c r="N29" t="n">
-        <v>108</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3145</v>
+        <v>1.4449</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8202</v>
+        <v>0.9016</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1097</v>
+        <v>0.1317</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3145</v>
+        <v>1.4449</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8515</v>
+        <v>1.4449</v>
       </c>
       <c r="G30" t="n">
-        <v>0.463</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8515</v>
+        <v>1.4449</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8594000000000001</v>
+        <v>1.4693</v>
       </c>
       <c r="J30" t="n">
-        <v>0.463</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="L30" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3224</v>
+        <v>1.4693</v>
       </c>
       <c r="N30" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2492</v>
+        <v>1.3738</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7795</v>
+        <v>0.8572</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0833</v>
+        <v>0.1034</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2492</v>
+        <v>1.3738</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2492</v>
+        <v>1.3738</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2492</v>
+        <v>1.3738</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2608</v>
+        <v>1.397</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2608</v>
+        <v>1.397</v>
       </c>
       <c r="N31" t="n">
         <v>108</v>
@@ -1872,461 +1872,461 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.194</v>
+        <v>1.3215</v>
       </c>
       <c r="C32" t="n">
-        <v>0.745</v>
+        <v>0.8246</v>
       </c>
       <c r="D32" t="n">
-        <v>0.061</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>1.194</v>
+        <v>1.3215</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3605</v>
+        <v>1.3215</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1665</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3605</v>
+        <v>1.3215</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3732</v>
+        <v>1.3326</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1665</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="L32" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2067</v>
+        <v>1.3326</v>
       </c>
       <c r="N32" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1196</v>
+        <v>1.3081</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6986</v>
+        <v>0.8162</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0309</v>
+        <v>0.0772</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1196</v>
+        <v>1.3081</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1196</v>
+        <v>0.8451</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1196</v>
+        <v>0.8451</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1353</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="K33" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1353</v>
+        <v>1.3224</v>
       </c>
       <c r="N33" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1059</v>
+        <v>1.2399</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0254</v>
+        <v>0.0501</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1059</v>
+        <v>1.2399</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1112</v>
+        <v>1.2399</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0053</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1112</v>
+        <v>1.2399</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1216</v>
+        <v>1.2608</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0053</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1163</v>
+        <v>1.2608</v>
       </c>
       <c r="N34" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.057</v>
+        <v>1.2213</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6595</v>
+        <v>0.762</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0056</v>
+        <v>0.0427</v>
       </c>
       <c r="E35" t="n">
-        <v>1.057</v>
+        <v>1.2213</v>
       </c>
       <c r="F35" t="n">
-        <v>1.057</v>
+        <v>1.0727</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.1486</v>
       </c>
       <c r="H35" t="n">
-        <v>1.057</v>
+        <v>1.0727</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0668</v>
+        <v>1.0908</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.1486</v>
       </c>
       <c r="K35" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0668</v>
+        <v>1.2394</v>
       </c>
       <c r="N35" t="n">
-        <v>117</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0261</v>
+        <v>1.1222</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6402</v>
+        <v>0.7002</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0068</v>
+        <v>0.0032</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0261</v>
+        <v>1.1222</v>
       </c>
       <c r="F36" t="n">
-        <v>1.6622</v>
+        <v>1.1275</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6361</v>
+        <v>-0.0053</v>
       </c>
       <c r="H36" t="n">
-        <v>1.6622</v>
+        <v>1.1275</v>
       </c>
       <c r="I36" t="n">
-        <v>1.6855</v>
+        <v>1.1466</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6361</v>
+        <v>-0.0053</v>
       </c>
       <c r="K36" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="L36" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0494</v>
+        <v>1.1413</v>
       </c>
       <c r="N36" t="n">
-        <v>230</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9721</v>
+        <v>1.1213</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6066</v>
+        <v>0.6996</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0287</v>
+        <v>0.0028</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9721</v>
+        <v>1.1213</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4915</v>
+        <v>1.1213</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4806</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4915</v>
+        <v>1.1213</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4984</v>
+        <v>1.1499</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4806</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>94</v>
       </c>
       <c r="L37" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9790000000000001</v>
+        <v>1.1499</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9497</v>
+        <v>1.0491</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5926</v>
+        <v>0.6546</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0377</v>
+        <v>-0.0259</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9497</v>
+        <v>1.0491</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8011</v>
+        <v>1.0491</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1486</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8011</v>
+        <v>1.0491</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8086</v>
+        <v>1.0668</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1486</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="L38" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9572000000000001</v>
+        <v>1.0668</v>
       </c>
       <c r="N38" t="n">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8449</v>
+        <v>1.0075</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5272</v>
+        <v>0.6286</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.08</v>
+        <v>-0.0425</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8449</v>
+        <v>1.0075</v>
       </c>
       <c r="F39" t="n">
-        <v>1.577</v>
+        <v>1.6436</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7321</v>
+        <v>-0.6361</v>
       </c>
       <c r="H39" t="n">
-        <v>1.577</v>
+        <v>1.6436</v>
       </c>
       <c r="I39" t="n">
-        <v>1.5917</v>
+        <v>1.6855</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7321</v>
+        <v>-0.6361</v>
       </c>
       <c r="K39" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="L39" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8595999999999999</v>
+        <v>1.0494</v>
       </c>
       <c r="N39" t="n">
-        <v>119</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.782</v>
+        <v>0.9741</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4879</v>
+        <v>0.6078</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1055</v>
+        <v>-0.0558</v>
       </c>
       <c r="E40" t="n">
-        <v>0.782</v>
+        <v>0.9741</v>
       </c>
       <c r="F40" t="n">
-        <v>0.782</v>
+        <v>0.9741</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.782</v>
+        <v>0.9741</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7967</v>
+        <v>0.9905</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7967</v>
+        <v>0.9905</v>
       </c>
       <c r="N40" t="n">
-        <v>209</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.771</v>
+        <v>0.9666</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4811</v>
+        <v>0.6031</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1099</v>
+        <v>-0.0588</v>
       </c>
       <c r="E41" t="n">
-        <v>0.771</v>
+        <v>0.9666</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7274</v>
+        <v>0.486</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0436</v>
+        <v>0.4806</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7274</v>
+        <v>0.486</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7376</v>
+        <v>0.4984</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0436</v>
+        <v>0.4806</v>
       </c>
       <c r="K41" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="L41" t="n">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7812</v>
+        <v>0.9790000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>230</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7373</v>
+        <v>0.872</v>
       </c>
       <c r="C42" t="n">
-        <v>0.46</v>
+        <v>0.5441</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1235</v>
+        <v>-0.0965</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7373</v>
+        <v>0.872</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4094</v>
+        <v>1.5441</v>
       </c>
       <c r="G42" t="n">
         <v>-0.6721</v>
       </c>
       <c r="H42" t="n">
-        <v>1.4094</v>
+        <v>1.5441</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4226</v>
+        <v>1.5702</v>
       </c>
       <c r="J42" t="n">
         <v>-0.6721</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7505000000000001</v>
+        <v>0.8981</v>
       </c>
       <c r="N42" t="n">
         <v>110</v>
@@ -2378,952 +2378,952 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7355</v>
+        <v>0.8011</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4589</v>
+        <v>0.4999</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1242</v>
+        <v>-0.1248</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7355</v>
+        <v>0.8011</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7355</v>
+        <v>0.7575</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7355</v>
+        <v>0.7575</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7768</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
       <c r="K43" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.8204</v>
       </c>
       <c r="N43" t="n">
-        <v>108</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6832</v>
+        <v>0.7704</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4263</v>
+        <v>0.4807</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1454</v>
+        <v>-0.137</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6832</v>
+        <v>0.7704</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6832</v>
+        <v>0.7704</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6832</v>
+        <v>0.7704</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6896</v>
+        <v>0.7967</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6896</v>
+        <v>0.7967</v>
       </c>
       <c r="N44" t="n">
-        <v>117</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.7301</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3538</v>
+        <v>0.4556</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1923</v>
+        <v>-0.153</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.7301</v>
       </c>
       <c r="F45" t="n">
-        <v>1.4822</v>
+        <v>0.7301</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.9152</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.4822</v>
+        <v>0.7301</v>
       </c>
       <c r="I45" t="n">
-        <v>1.503</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9152</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5877999999999999</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>167</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1346</v>
+        <v>0.6781</v>
       </c>
       <c r="C46" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4231</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.367</v>
+        <v>-0.1738</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1346</v>
+        <v>0.6781</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1346</v>
+        <v>0.6781</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1346</v>
+        <v>0.6781</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1352</v>
+        <v>0.6896</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1352</v>
+        <v>0.6896</v>
       </c>
       <c r="N46" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0867</v>
+        <v>0.3007</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0541</v>
+        <v>0.1876</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3863</v>
+        <v>-0.3241</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0867</v>
+        <v>0.3007</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0867</v>
+        <v>1.3007</v>
       </c>
       <c r="G47" t="n">
         <v>-1</v>
       </c>
       <c r="H47" t="n">
-        <v>1.0867</v>
+        <v>1.3007</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1019</v>
+        <v>1.3227</v>
       </c>
       <c r="J47" t="n">
         <v>-1</v>
       </c>
       <c r="K47" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="L47" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1019000000000001</v>
+        <v>0.3227</v>
       </c>
       <c r="N47" t="n">
-        <v>167</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0592</v>
+        <v>0.1341</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0369</v>
+        <v>0.0837</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3974</v>
+        <v>-0.3905</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0592</v>
+        <v>0.1341</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0592</v>
+        <v>0.1341</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0592</v>
+        <v>0.1341</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0598</v>
+        <v>0.1352</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0598</v>
+        <v>0.1352</v>
       </c>
       <c r="N48" t="n">
-        <v>161</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.3536</v>
+        <v>0.1169</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2206</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5642</v>
+        <v>-0.3973</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3536</v>
+        <v>0.1169</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3536</v>
+        <v>1.1169</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.3536</v>
+        <v>1.1169</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3536</v>
+        <v>1.1453</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K49" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.3536</v>
+        <v>0.1453</v>
       </c>
       <c r="N49" t="n">
-        <v>65</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.4129</v>
+        <v>-0.3536</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2576</v>
+        <v>-0.2206</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5848</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.4129</v>
+        <v>-0.3536</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4129</v>
+        <v>-0.3536</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4129</v>
+        <v>-0.3536</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4148</v>
+        <v>-0.3536</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.4148</v>
+        <v>-0.3536</v>
       </c>
       <c r="N50" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.4215</v>
+        <v>-0.4113</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.263</v>
+        <v>-0.2566</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5916</v>
+        <v>-0.6078</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.4215</v>
+        <v>-0.4113</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4215</v>
+        <v>-0.4113</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4215</v>
+        <v>-0.4113</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4235</v>
+        <v>-0.4148</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.4235</v>
+        <v>-0.4148</v>
       </c>
       <c r="N51" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.4572</v>
+        <v>-0.42</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2853</v>
+        <v>-0.2621</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6061</v>
+        <v>-0.6112</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.4572</v>
+        <v>-0.42</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.4572</v>
+        <v>-0.42</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.4572</v>
+        <v>-0.42</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.4615</v>
+        <v>-0.4235</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.4615</v>
+        <v>-0.4235</v>
       </c>
       <c r="N52" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.5261</v>
+        <v>-0.4538</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3283</v>
+        <v>-0.2832</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6339</v>
+        <v>-0.6247</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5261</v>
+        <v>-0.4538</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.5261</v>
+        <v>-0.4538</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5261</v>
+        <v>-0.4538</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.531</v>
+        <v>-0.4615</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.531</v>
+        <v>-0.4615</v>
       </c>
       <c r="N53" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5027</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.35</v>
+        <v>-0.3137</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.648</v>
+        <v>-0.6442</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5027</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2271</v>
+        <v>-0.5027</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3339</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2271</v>
+        <v>-0.5027</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2292</v>
+        <v>-0.5069</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.3339</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="L54" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.5630999999999999</v>
+        <v>-0.5069</v>
       </c>
       <c r="N54" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.5617</v>
+        <v>-0.5222</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3505</v>
+        <v>-0.3258</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6483</v>
+        <v>-0.652</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5617</v>
+        <v>-0.5222</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4383</v>
+        <v>-0.5222</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4383</v>
+        <v>-0.5222</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4424</v>
+        <v>-0.531</v>
       </c>
       <c r="J55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="L55" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.5576</v>
+        <v>-0.531</v>
       </c>
       <c r="N55" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.5763</v>
+        <v>-0.5593</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3596</v>
+        <v>-0.349</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6542</v>
+        <v>-0.6667</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5763</v>
+        <v>-0.5593</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.5763</v>
+        <v>-0.2254</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.3339</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.5763</v>
+        <v>-0.2254</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.579</v>
+        <v>-0.2292</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.3339</v>
       </c>
       <c r="K56" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.579</v>
+        <v>-0.5630999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.6484</v>
+        <v>-0.5742</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4046</v>
+        <v>-0.3583</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6833</v>
+        <v>-0.6727</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.6484</v>
+        <v>-0.5742</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.6484</v>
+        <v>-0.5742</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.6484</v>
+        <v>-0.5742</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6544</v>
+        <v>-0.579</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.6544</v>
+        <v>-0.579</v>
       </c>
       <c r="N57" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.6761</v>
+        <v>-0.6435</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4219</v>
+        <v>-0.4015</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6945</v>
+        <v>-0.7003</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.6761</v>
+        <v>-0.6435</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.6761</v>
+        <v>-0.6435</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.6761</v>
+        <v>-0.6435</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.6761</v>
+        <v>-0.6544</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>65</v>
+        <v>161</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.6761</v>
+        <v>-0.6544</v>
       </c>
       <c r="N58" t="n">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.7164</v>
+        <v>-0.6761</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.447</v>
+        <v>-0.4219</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7108</v>
+        <v>-0.7133</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.7164</v>
+        <v>-0.6761</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.7164</v>
+        <v>-0.6761</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.7164</v>
+        <v>-0.6761</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.7231</v>
+        <v>-0.6761</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.7231</v>
+        <v>-0.6761</v>
       </c>
       <c r="N59" t="n">
-        <v>117</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.717</v>
+        <v>-0.7111</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.4474</v>
+        <v>-0.4437</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.711</v>
+        <v>-0.7272</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.717</v>
+        <v>-0.7111</v>
       </c>
       <c r="F60" t="n">
+        <v>-0.7111</v>
+      </c>
+      <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="G60" t="n">
-        <v>-0.717</v>
-      </c>
       <c r="H60" t="n">
+        <v>-0.7111</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.7231</v>
+      </c>
+      <c r="J60" t="n">
         <v>0</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
+        <v>117</v>
+      </c>
+      <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="n">
-        <v>-0.717</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>123</v>
-      </c>
       <c r="M60" t="n">
-        <v>-0.717</v>
+        <v>-0.7231</v>
       </c>
       <c r="N60" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.8398</v>
+        <v>-0.717</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.524</v>
+        <v>-0.4474</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.7296</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.8398</v>
+        <v>-0.717</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.8398</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>-0.717</v>
+      </c>
+      <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="n">
-        <v>-0.8398</v>
-      </c>
       <c r="I61" t="n">
-        <v>-0.8437</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
+        <v>-0.717</v>
+      </c>
+      <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="n">
-        <v>103</v>
-      </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.8437</v>
+        <v>-0.717</v>
       </c>
       <c r="N61" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>crisby</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8486</v>
+        <v>-0.737</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5295</v>
+        <v>-0.4599</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7642</v>
+        <v>-0.7375</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8486</v>
+        <v>-0.737</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.8486</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-1.4321</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.8486</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.8486</v>
+        <v>0.7068</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-1.4321</v>
       </c>
       <c r="K62" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.8486</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>65</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8517</v>
+        <v>-0.8367</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.5314</v>
+        <v>-0.5221</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7654</v>
+        <v>-0.7773</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8517</v>
+        <v>-0.8367</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.8517</v>
+        <v>-0.8367</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.8517</v>
+        <v>-0.8367</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.8557</v>
+        <v>-0.8437</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.8557</v>
+        <v>-0.8437</v>
       </c>
       <c r="N63" t="n">
         <v>103</v>
@@ -3344,185 +3344,185 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>crisby</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8862</v>
+        <v>-0.8486</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.553</v>
+        <v>-0.5295</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7794</v>
+        <v>-0.782</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8862</v>
+        <v>-0.8486</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8862</v>
+        <v>-0.8486</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.8862</v>
+        <v>-0.8486</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.8903</v>
+        <v>-0.8486</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.8903</v>
+        <v>-0.8486</v>
       </c>
       <c r="N64" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8829</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5532</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7795</v>
+        <v>-0.7957</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8829</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8829</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.8829</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8907</v>
+        <v>-0.8903</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8907</v>
+        <v>-0.8903</v>
       </c>
       <c r="N65" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.9035</v>
+        <v>-0.8833</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5637</v>
+        <v>-0.5511</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7864</v>
+        <v>-0.7958</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.9035</v>
+        <v>-0.8833</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9035</v>
+        <v>-0.8833</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9035</v>
+        <v>-0.8833</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9035</v>
+        <v>-0.8907</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.9035</v>
+        <v>-0.8907</v>
       </c>
       <c r="N66" t="n">
-        <v>54</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9308</v>
+        <v>-0.9035</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5808</v>
+        <v>-0.5637</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7974</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9308</v>
+        <v>-0.9035</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5013</v>
+        <v>-0.9035</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.4321</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5013</v>
+        <v>-0.9035</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5059</v>
+        <v>-0.9035</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.4321</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L67" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.9261999999999999</v>
+        <v>-0.9035</v>
       </c>
       <c r="N67" t="n">
-        <v>253</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
@@ -3538,7 +3538,7 @@
         <v>-0.6233</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8249</v>
+        <v>-0.8419</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9989</v>
@@ -3584,7 +3584,7 @@
         <v>-0.624</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E69" t="n">
         <v>-1</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6449</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8389</v>
+        <v>-0.8557</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0335</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0799</v>
+        <v>-1.0758</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6738</v>
+        <v>-0.6713</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8576</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0799</v>
+        <v>-1.0758</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.0799</v>
+        <v>-1.0758</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.0799</v>
+        <v>-1.0758</v>
       </c>
       <c r="I71" t="n">
         <v>-1.0849</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1626</v>
+        <v>-1.1583</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7254</v>
+        <v>-0.7227</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.891</v>
+        <v>-0.9054</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1626</v>
+        <v>-1.1583</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.1626</v>
+        <v>-1.1583</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.1626</v>
+        <v>-1.1583</v>
       </c>
       <c r="I72" t="n">
         <v>-1.168</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.3671</v>
+        <v>-1.362</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.853</v>
+        <v>-0.8498</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9736</v>
+        <v>-0.9865</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.3671</v>
+        <v>-1.362</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.3671</v>
+        <v>-1.362</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.3671</v>
+        <v>-1.362</v>
       </c>
       <c r="I73" t="n">
         <v>-1.3735</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8611</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9789</v>
+        <v>-0.9937</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3801</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.4242</v>
+        <v>-1.4189</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.8853</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9967</v>
+        <v>-1.0092</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.4242</v>
+        <v>-1.4189</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.4242</v>
+        <v>-1.4189</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.4242</v>
+        <v>-1.4189</v>
       </c>
       <c r="I75" t="n">
         <v>-1.4308</v>
@@ -3906,7 +3906,7 @@
         <v>-0.929</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0228</v>
+        <v>-1.0371</v>
       </c>
       <c r="E76" t="n">
         <v>-1.4889</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5728</v>
+        <v>-1.5669</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.9777</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0567</v>
+        <v>-1.0682</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5728</v>
+        <v>-1.5669</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5728</v>
+        <v>-1.5669</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5728</v>
+        <v>-1.5669</v>
       </c>
       <c r="I77" t="n">
         <v>-1.5801</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5994</v>
+        <v>-1.5898</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.998</v>
+        <v>-0.992</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0675</v>
+        <v>-1.0773</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5994</v>
+        <v>-1.5898</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.2874</v>
+        <v>-1.2778</v>
       </c>
       <c r="G78" t="n">
         <v>-0.312</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.2874</v>
+        <v>-1.2778</v>
       </c>
       <c r="I78" t="n">
         <v>-1.2994</v>
@@ -4044,7 +4044,7 @@
         <v>-1.0194</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0814</v>
+        <v>-1.0948</v>
       </c>
       <c r="E79" t="n">
         <v>-1.6338</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0904</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1273</v>
+        <v>-1.1401</v>
       </c>
       <c r="E80" t="n">
         <v>-1.7475</v>
@@ -4136,7 +4136,7 @@
         <v>-1.2245</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2142</v>
+        <v>-1.2258</v>
       </c>
       <c r="E81" t="n">
         <v>-1.9625</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.1043</v>
+        <v>-2.0965</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.313</v>
+        <v>-1.3081</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.2715</v>
+        <v>-1.2792</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.1043</v>
+        <v>-2.0965</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.1043</v>
+        <v>-2.0965</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.1043</v>
+        <v>-2.0965</v>
       </c>
       <c r="I82" t="n">
         <v>-2.1141</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-2.5154</v>
+        <v>-2.5078</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.5695</v>
+        <v>-1.5648</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.4375</v>
+        <v>-1.443</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.5154</v>
+        <v>-2.5078</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.5154</v>
+        <v>-0.5078</v>
       </c>
       <c r="G83" t="n">
         <v>-2</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.5154</v>
+        <v>-0.5078</v>
       </c>
       <c r="I83" t="n">
         <v>-0.5251</v>
